--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136693248</v>
+        <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>91905</v>
+        <v>92906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1067</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>blandskog på blockmark, Sk</t>
+          <t>Blandskog, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380975</v>
+        <v>381036</v>
       </c>
       <c r="R2" t="n">
-        <v>6246756</v>
+        <v>6246770</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +756,16 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>intill bok</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -777,62 +782,57 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136693248</t>
+          <t>https://artportalen.se/Sighting/136699058</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136692815</v>
+        <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>91906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hässlebo blandskog, Vallåsens gamla domänreservat, Sk</t>
+          <t>bergsknalle med blockmark, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>381097</v>
+        <v>380974</v>
       </c>
       <c r="R3" t="n">
-        <v>6246707</v>
+        <v>6246755</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,6 +867,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på knäckt toppgren av bok</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,59 +900,54 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692815</t>
+          <t>https://artportalen.se/Sighting/136693248</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136688476</v>
+        <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>91906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Rösjön 4, Sk</t>
+          <t>O Djurholmen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380983</v>
+        <v>381109</v>
       </c>
       <c r="R4" t="n">
-        <v>6246775</v>
+        <v>6246716</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,22 +971,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många på låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,66 +1017,58 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136688476</t>
+          <t>https://artportalen.se/Sighting/136703847</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136692554</v>
+        <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>58165</v>
+        <v>96931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Alkärr, öppet vatten, Vallåsens gamla domänreservat, Sk</t>
+          <t>Hässlebo blandskog, Vallåsens gamla domänreservat, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>381190</v>
+        <v>381097</v>
       </c>
       <c r="R5" t="n">
-        <v>6246779</v>
+        <v>6246707</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,36 +1121,40 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692554</t>
+          <t>https://artportalen.se/Sighting/136692815</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136693161</v>
+        <v>136688476</v>
       </c>
       <c r="B6" t="n">
-        <v>58165</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,32 +1162,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>blandskog på blockmark, Sk</t>
+          <t>N Rösjön 4, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380975</v>
+        <v>380983</v>
       </c>
       <c r="R6" t="n">
-        <v>6246756</v>
+        <v>6246775</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,9 +1207,19 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,20 +1234,248 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136688476</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136692554</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58165</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alkärr, öppet vatten, Vallåsens gamla domänreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>381190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6246779</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136692554</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136693161</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58165</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>blandskog på blockmark, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>380975</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6246756</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136693161</t>
         </is>
@@ -1255,6 +1488,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1408,14 +1408,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>blandskog på blockmark, Sk</t>
+          <t>bergsknalle med blockmark, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380975</v>
+        <v>380974</v>
       </c>
       <c r="R8" t="n">
-        <v>6246756</v>
+        <v>6246755</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91906</v>
+        <v>91911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91906</v>
+        <v>91911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136688476</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>136692554</v>
       </c>
       <c r="B7" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>136693161</v>
       </c>
       <c r="B8" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91911</v>
+        <v>91913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91911</v>
+        <v>91913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91915</v>
+        <v>91917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91915</v>
+        <v>91917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136688476</v>
+        <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>96957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,42 +1145,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Rösjön 4, Sk</t>
+          <t>Sjöalt Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380983</v>
+        <v>381107</v>
       </c>
       <c r="R6" t="n">
-        <v>6246775</v>
+        <v>6246704</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,44 +1229,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136688476</t>
+          <t>https://artportalen.se/Sighting/137150152</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136692554</v>
+        <v>136688476</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1279,32 +1274,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Alkärr, öppet vatten, Vallåsens gamla domänreservat, Sk</t>
+          <t>N Rösjön 4, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>381190</v>
+        <v>380983</v>
       </c>
       <c r="R7" t="n">
-        <v>6246779</v>
+        <v>6246775</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,9 +1319,19 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,44 +1346,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136692554</t>
+          <t>https://artportalen.se/Sighting/136688476</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136693161</v>
+        <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1393,32 +1391,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>bergsknalle med blockmark, Sk</t>
+          <t>Sjöalt Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380974</v>
+        <v>380983</v>
       </c>
       <c r="R8" t="n">
-        <v>6246755</v>
+        <v>6246766</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,9 +1431,19 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,14 +1466,578 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150173</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136692554</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alkärr, öppet vatten, Vallåsens gamla domänreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>381190</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6246779</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136692554</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136693161</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>bergsknalle med blockmark, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>380974</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6246755</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136693161</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137150170</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjöalt Hallandsåsen, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>380977</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6246750</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150170</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137150181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjöalt Hallandsåsen, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>381184</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6246794</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150181</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137150180</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjöalt Hallandsåsen, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>381191</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6246794</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150180</t>
         </is>
       </c>
     </row>
@@ -1490,6 +2050,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>91943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>91943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136688476</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>136692554</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>136693161</v>
       </c>
       <c r="B10" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>136688476</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>136692554</v>
       </c>
       <c r="B9" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>136693161</v>
       </c>
       <c r="B10" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1275,11 +1275,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>N Rösjön 4, Sk</t>
@@ -1510,11 +1506,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1624,11 +1616,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91945</v>
+        <v>91948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91945</v>
+        <v>91948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136692815</v>
       </c>
       <c r="B5" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136699058</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136693248</v>
       </c>
       <c r="B3" t="n">
-        <v>91948</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136703847</v>
       </c>
       <c r="B4" t="n">
-        <v>91948</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35680-2026 artfynd.xlsx
+++ b/artfynd/A 35680-2026 artfynd.xlsx
@@ -1137,7 +1137,7 @@
         <v>137150152</v>
       </c>
       <c r="B6" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137150173</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>137150170</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>137150181</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137150180</v>
       </c>
       <c r="B13" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
